--- a/Official Only Whitelist.xlsx
+++ b/Official Only Whitelist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04165F6-DA8A-4667-86EE-12A809446782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DDE13D-0AD1-4347-BA00-4344EBEE1EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1060" yWindow="1060" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Title</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/scenes-from-a-marriage/</t>
+  </si>
+  <si>
+    <t>It&amp;#039;s Such a Beautiful Day</t>
   </si>
 </sst>
 </file>
@@ -406,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.54296875" bestFit="1" customWidth="1"/>
@@ -460,9 +463,24 @@
         <v>9</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>2012</v>
+      </c>
+      <c r="C5">
+        <v>489412</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{D022377C-DECA-4C97-BD30-AFF1A3BBE81B}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{D6B3167E-0C0B-414A-864C-BAB8CE7872BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
